--- a/output/pdf_financials_xlsx/GMIN.xlsx
+++ b/output/pdf_financials_xlsx/GMIN.xlsx
@@ -3277,13 +3277,13 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.06500499999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.901192</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.248228</v>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.143</v>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
@@ -4053,13 +4053,13 @@
         <v>-0.147615</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-3.314417</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.298793</v>
+        <v>-13.424312</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-4.148389</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
@@ -6257,7 +6257,11 @@
           <t>Share-based Payments Reserve 16 19,433</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -7299,7 +7303,11 @@
           <t>Share-based Payments Reserve (note 10)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -7766,7 +7774,11 @@
           <t>Share-based Payments Reserve (note 9)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -11098,7 +11110,11 @@
           <t>Exploration and Evaluation Expenditures 6</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -12520,7 +12536,11 @@
           <t>Exploration and Evaluation Expenditures</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GMIN.xlsx
+++ b/output/pdf_financials_xlsx/GMIN.xlsx
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.06411600000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.778986</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>57.503632</v>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.06411600000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.778986</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>57.503632</v>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.06411600000000001</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.778986</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>3.105393</v>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.788</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
@@ -1876,10 +1876,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G49" s="3" t="n">
+        <v>1.788</v>
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
@@ -2308,10 +2306,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G62" s="3" t="n">
+        <v>585.917</v>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
@@ -4887,7 +4883,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -7509,7 +7505,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
